--- a/financial_advisor_forms/005_uniform_borrower_assistance_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/005_uniform_borrower_assistance_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1178,8 +1178,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'financially_stable'}</t>
+          <t>financially_stable</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Financially Stable'}</t>
+          <t>Financially Stable</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'financially_struggling'}</t>
+          <t>financially_struggling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Financially Struggling'}</t>
+          <t>Financially Struggling</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'financially_distressed'}</t>
+          <t>financially_distressed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Financially Distressed'}</t>
+          <t>Financially Distressed</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employment_income'}</t>
+          <t>employment_income</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employment Income'}</t>
+          <t>Employment Income</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'social_security'}</t>
+          <t>social_security</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Social Security'}</t>
+          <t>Social Security</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pensions'}</t>
+          <t>pensions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pensions'}</t>
+          <t>Pensions</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_employed'}</t>
+          <t>not_employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Employed'}</t>
+          <t>Not Employed</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retiree'}</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retiree'}</t>
+          <t>Retiree</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'income_qualified'}</t>
+          <t>income_qualified</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Income Qualified'}</t>
+          <t>Income Qualified</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'income_ineligible'}</t>
+          <t>income_ineligible</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Income Ineligible'}</t>
+          <t>Income Ineligible</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bank_of_america'}</t>
+          <t>bank_of_america</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bank of America'}</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wells_fargo'}</t>
+          <t>wells_fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wells Fargo'}</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'primary_residence'}</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Primary Residence'}</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'second_home'}</t>
+          <t>second_home</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Second Home'}</t>
+          <t>Second Home</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'investment_property'}</t>
+          <t>investment_property</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Investment Property'}</t>
+          <t>Investment Property</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'collateral'}</t>
+          <t>collateral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Collateral'}</t>
+          <t>Collateral</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unsecured'}</t>
+          <t>unsecured</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unsecured'}</t>
+          <t>Unsecured</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
